--- a/uploader/docs/DBA제출_컬럼정의_2026-09-08.xlsx
+++ b/uploader/docs/DBA제출_컬럼정의_2026-09-08.xlsx
@@ -10,7 +10,7 @@
     <sheet name="컬럼정의" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'컬럼정의'!$A$1:$N$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'컬럼정의'!$A$1:$N$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -624,7 +624,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>명250</t>
+          <t>명40</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>내용800</t>
+          <t>내용600</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>분류가 끝나면 값이 바뀐다(미분류 폴더 → classified/{기관구분}/{문서년}/{기관명}/). 최악 경로가 약 591자라 800 으로 잡았다</t>
+          <t>분류가 끝나면 값이 바뀐다(미분류 폴더 → classified/{기관구분}/{문서년}/{기관명}/). 기관명이 40자로 줄어 최악 경로가 약 341자다. 인포타입에 400 이 없어 600 으로 잡았다</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>명250</t>
+          <t>명40</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>수정일시</t>
+          <t>협약기관상태구분</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>수정일시</t>
+          <t>협약기관상태구분코드</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>일시20</t>
+          <t>구분코드2</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1229,29 +1229,245 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULLABLE</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="4" t="inlineStr">
         <is>
+          <t>해당 기관과 협약이 체결되었는지 여부</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>01 미협약 / 02 협약. ⚠️ 애플리케이션이 읽지도 쓰지도 않는다 — 기관 정보를 미리 담아 둘 자리다</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TSKGIAF02</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>입찰공고상태</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>입찰공고상태구분코드</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>구분코드2</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>CHARACTER</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>NULLABLE</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>해당 기관의 입찰공고 진행 상태</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>01 공고전 / 02 공고중 / 03 공고완료. ⚠️ 애플리케이션 미사용(위와 같음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TSKGIAF02</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>입찰공고시작</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>입찰공고시작년월일</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>년월일8</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>CHARACTER</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>NULLABLE</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>입찰공고 시작일</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>YYYYMMDD 8자리. ⚠️ 애플리케이션 미사용(위와 같음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>TSKGIAF02</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>입찰공고마감</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>입찰공고마감년월일</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>년월일8</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>CHARACTER</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>NULLABLE</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>입찰공고 마감일</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>YYYYMMDD 8자리. ⚠️ 애플리케이션 미사용(위와 같음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TSKGIAF02</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>수정일시</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>수정일시</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>일시14</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>CHARACTER</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
           <t>기관 정보가 마지막으로 수정된 시각</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>YYYYMMDDHH24MISS</t>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>YYYYMMDDHH24MISS 14자. 인포타입 길이가 형식과 정확히 일치한다</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N14"/>
+  <autoFilter ref="A1:N18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/uploader/docs/DBA제출_컬럼정의_2026-09-08.xlsx
+++ b/uploader/docs/DBA제출_컬럼정의_2026-09-08.xlsx
@@ -662,12 +662,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>기관구분</t>
+          <t>기관영업분류</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>기관구분코드</t>
+          <t>기관영업분류구분코드</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -699,7 +699,7 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>기관의 유형 코드. TSKGIAF02.기관구분 에서 복사되어 들어온다</t>
+          <t>기관의 유형 코드. TSKGIAF02.기관영업분류 에서 복사되어 들어온다</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>일시20</t>
+          <t>일시14</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>YYYYMMDDHH24MISS 14자를 채운다(20자는 여유). 자릿수가 고정이라 문자열 정렬이 곧 시간 정렬이다</t>
+          <t>YYYYMMDDHH24MISS 14자. 자릿수가 고정이라 문자열 정렬이 곧 시간 정렬이다</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>일시20</t>
+          <t>일시14</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>분류가 끝나면 값이 바뀐다(미분류 폴더 → classified/{기관구분}/{문서년}/{기관명}/). 기관명이 40자로 줄어 최악 경로가 약 341자다. 인포타입에 400 이 없어 600 으로 잡았다</t>
+          <t>분류가 끝나면 값이 바뀐다(미분류 폴더 → classified/{기관영업분류}/{문서년}/{기관명}/). 기관명이 40자로 줄어 최악 경로가 약 341자다. 인포타입에 400 이 없어 600 으로 잡았다</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>기관구분</t>
+          <t>기관영업분류</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>기관구분코드</t>
+          <t>기관영업분류구분코드</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">

--- a/uploader/docs/DBA제출_컬럼정의_2026-09-08.xlsx
+++ b/uploader/docs/DBA제출_컬럼정의_2026-09-08.xlsx
@@ -662,12 +662,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>기관영업분류</t>
+          <t>기관영업분류코드</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>기관영업분류구분코드</t>
+          <t>기관영업분류코드</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -678,7 +678,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>구분코드2</t>
+          <t>코드2</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -699,7 +699,7 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>기관의 유형 코드. TSKGIAF02.기관영업분류 에서 복사되어 들어온다</t>
+          <t>기관의 유형 코드. TSKGIAF02.기관영업분류코드 에서 복사되어 들어온다</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>분류가 끝나면 값이 바뀐다(미분류 폴더 → classified/{기관영업분류}/{문서년}/{기관명}/). 기관명이 40자로 줄어 최악 경로가 약 341자다. 인포타입에 400 이 없어 600 으로 잡았다</t>
+          <t>분류가 끝나면 값이 바뀐다(미분류 폴더 → classified/{기관영업분류코드}/{문서년}/{기관명}/). 기관명이 40자로 줄어 최악 경로가 약 341자다. 인포타입에 400 이 없어 600 으로 잡았다</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>기관영업분류</t>
+          <t>기관영업분류코드</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>기관영업분류구분코드</t>
+          <t>기관영업분류코드</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>구분코드2</t>
+          <t>코드2</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">

--- a/uploader/docs/DBA제출_컬럼정의_2026-09-08.xlsx
+++ b/uploader/docs/DBA제출_컬럼정의_2026-09-08.xlsx
@@ -10,7 +10,7 @@
     <sheet name="컬럼정의" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'컬럼정의'!$A$1:$N$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'컬럼정의'!$A$1:$N$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>기본키. 애플리케이션이 시퀀스 TSKGIAF01_SEQ 에서 채번해 직접 입력한다(IDENTITY 미사용)</t>
+          <t>기본키. 애플리케이션이 시퀀스 SQ_KGI_AGENTFILETABLE 에서 채번해 직접 입력한다(IDENTITY 미사용)</t>
         </is>
       </c>
     </row>
@@ -662,12 +662,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>기관영업분류코드</t>
+          <t>기관영업분류구분</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>기관영업분류코드</t>
+          <t>기관영업분류구분코드</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -678,7 +678,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>코드2</t>
+          <t>구분코드2</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -699,7 +699,7 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>기관의 유형 코드. TSKGIAF02.기관영업분류코드 에서 복사되어 들어온다</t>
+          <t>기관의 영업 분류 코드. TSKGIAF02.기관영업분류구분 에서 복사되어 들어온다</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>파일시스템 상한이 255자(NTFS·ext4)라 260 으로 잡았다. 한글·공백·괄호가 그대로 들어온다</t>
+          <t>파일시스템 상한이 255자(NTFS·ext4)인데 인포타입에 255 가 없어 260 으로 잡았다</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>파일이 업로드된 시각</t>
+          <t>파일이 업로드된 시각. **업무 시각**이다</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>저장경로</t>
+          <t>저장경로내용</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1028,117 +1028,115 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>분류가 끝나면 값이 바뀐다(미분류 폴더 → classified/{기관영업분류코드}/{문서년}/{기관명}/). 기관명이 40자로 줄어 최악 경로가 약 341자다. 인포타입에 400 이 없어 600 으로 잡았다</t>
+          <t>분류가 끝나면 값이 바뀐다(미분류 폴더 → classified/{기관영업분류구분}/{문서년}/{기관명}/). 최악 경로가 약 341자다</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TSKGIAF02</t>
+          <t>TSKGIAF01</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>기관일련번호</t>
+          <t>시스템사용일시</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>기관일련번호</t>
+          <t>시스템사용일시</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>일련번호16</t>
+          <t>일시14</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>DECIMAL</t>
+          <t>CHARACTER</t>
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULLABLE</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>기관 1건을 식별하는 일련번호</t>
+          <t>이 행을 마지막으로 건드린 시각. 업로드일시(업무 시각)와 다른 **감사 시각**이다</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>기본키. 애플리케이션이 시퀀스 TSKGIAF02_SEQ 에서 채번해 직접 입력한다</t>
+          <t>INSERT 는 업로드일시와 같은 값, 분류 UPDATE 는 분류일시와 같은 값, 삭제·반려는 그 시점의 DB 시각을 넣는다</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TSKGIAF02</t>
+          <t>TSKGIAF01</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>기관명</t>
+          <t>시스템사용자번호</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>기관명</t>
+          <t>시스템사용자번호</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>명40</t>
+          <t>사용자번호7</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
+          <t>CHARACTER</t>
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULLABLE</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>기관의 이름</t>
+          <t>이 데이터를 넣게 만든 주체. 사람이 아니라 프로그램이다</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>UNIQUE 제약. TSKGIAF01.기관명 과 대조하는 실질 키라 중복이 있으면 분류가 어긋난다</t>
+          <t>화면번호에서 앞 K 를 뗀 7자(KGI11100 → GI11100). 재분류 배치는 'BATCH01'. 컨트롤러 클래스명에서 자동으로 도출한다</t>
         </is>
       </c>
     </row>
@@ -1150,34 +1148,36 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>기관영업분류코드</t>
+          <t>기관일련번호</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>기관영업분류코드</t>
+          <t>기관일련번호</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>코드2</t>
+          <t>일련번호16</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>CHARACTER</t>
+          <t>DECIMAL</t>
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
           <t>NOT NULL</t>
@@ -1187,12 +1187,12 @@
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>기관의 유형 코드. 이 값이 파일의 분류 결과가 된다</t>
+          <t>기관 1건을 식별하는 일련번호</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>01 지방자치단체 / 02 공공기관 / 03 대학교 / 04 병원 / 05 법원</t>
+          <t>기본키. 애플리케이션이 시퀀스 SQ_KGI_AGENTGIGANTABLE 에서 채번해 직접 입력한다</t>
         </is>
       </c>
     </row>
@@ -1204,49 +1204,49 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>협약기관상태구분</t>
+          <t>기관명</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>협약기관상태구분코드</t>
+          <t>기관명</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>구분코드2</t>
+          <t>명40</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>CHARACTER</t>
+          <t>VARCHAR</t>
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>NULLABLE</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>해당 기관과 협약이 체결되었는지 여부</t>
+          <t>기관의 이름</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>01 미협약 / 02 협약. ⚠️ 애플리케이션이 읽지도 쓰지도 않는다 — 기관 정보를 미리 담아 둘 자리다</t>
+          <t>UNIQUE 제약. TSKGIAF01.기관명 과 대조하는 실질 키라 중복이 있으면 분류가 어긋난다</t>
         </is>
       </c>
     </row>
@@ -1258,16 +1258,16 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>입찰공고상태</t>
+          <t>기관영업분류구분</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>입찰공고상태구분코드</t>
+          <t>기관영업분류구분코드</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -1288,19 +1288,19 @@
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>NULLABLE</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>해당 기관의 입찰공고 진행 상태</t>
+          <t>기관의 영업 분류 코드. 이 값이 파일의 분류 결과가 된다</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>01 공고전 / 02 공고중 / 03 공고완료. ⚠️ 애플리케이션 미사용(위와 같음)</t>
+          <t>01 지방자치단체 / 02 공공기관 / 03 대학교 / 04 병원 / 05 법원</t>
         </is>
       </c>
     </row>
@@ -1312,23 +1312,23 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>입찰공고시작</t>
+          <t>협약기관상태구분</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>입찰공고시작년월일</t>
+          <t>협약기관상태구분코드</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>년월일8</t>
+          <t>구분코드2</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr">
@@ -1349,12 +1349,12 @@
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>입찰공고 시작일</t>
+          <t>해당 기관과 협약이 체결되었는지 여부</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>YYYYMMDD 8자리. ⚠️ 애플리케이션 미사용(위와 같음)</t>
+          <t>01 미협약 / 02 협약. 애플리케이션이 읽지도 쓰지도 않는다 — 미리 담아 둘 자리다</t>
         </is>
       </c>
     </row>
@@ -1366,23 +1366,23 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>입찰공고마감</t>
+          <t>입찰공고상태구분</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>입찰공고마감년월일</t>
+          <t>입찰공고상태구분코드</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>년월일8</t>
+          <t>구분코드2</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr">
@@ -1403,12 +1403,12 @@
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>입찰공고 마감일</t>
+          <t>해당 기관의 입찰공고 진행 상태</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>YYYYMMDD 8자리. ⚠️ 애플리케이션 미사용(위와 같음)</t>
+          <t>01 공고전 / 02 공고중 / 03 공고완료. 애플리케이션 미사용(위와 같음)</t>
         </is>
       </c>
     </row>
@@ -1420,54 +1420,216 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>수정일시</t>
+          <t>입찰공고시작년월일</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>수정일시</t>
+          <t>입찰공고시작년월일</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>년월일8</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>CHARACTER</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
         <v>8</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>일시14</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>CHARACTER</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>14</v>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULLABLE</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>기관 정보가 마지막으로 수정된 시각</t>
+          <t>입찰공고 시작일</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>YYYYMMDDHH24MISS 14자. 인포타입 길이가 형식과 정확히 일치한다</t>
+          <t>YYYYMMDD 8자리. 애플리케이션 미사용(위와 같음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TSKGIAF02</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>입찰공고마감년월일</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>입찰공고마감년월일</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>년월일8</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>CHARACTER</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>NULLABLE</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>입찰공고 마감일</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>YYYYMMDD 8자리. 애플리케이션 미사용(위와 같음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TSKGIAF02</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>시스템사용일시</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>시스템사용일시</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>일시14</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>CHARACTER</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>기관 정보를 마지막으로 건드린 시각</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>YYYYMMDDHH24MISS 14자. **옛 `수정일시` 가 이 이름으로 바뀐 것**이라 TSKGIAF01 쪽과 달리 NOT NULL 이다</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TSKGIAF02</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>시스템사용자번호</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>시스템사용자번호</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>사용자번호7</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>CHARACTER</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>NULLABLE</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>이 데이터를 넣게 만든 주체</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>화면번호에서 앞 K 를 뗀 7자(KGI13100 → GI13100). 대량 반입은 GI13400·GI13410</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N18"/>
+  <autoFilter ref="A1:N21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>